--- a/artfynd/A 459-2022 artfynd.xlsx
+++ b/artfynd/A 459-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121899388</v>
+        <v>121899387</v>
       </c>
       <c r="B2" t="n">
-        <v>74714</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121899387</v>
+        <v>121899388</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>74727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Björkstubbe</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Björkstubbe</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 459-2022 artfynd.xlsx
+++ b/artfynd/A 459-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>121899388</v>
       </c>
       <c r="B3" t="n">
-        <v>74727</v>
+        <v>74729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 459-2022 artfynd.xlsx
+++ b/artfynd/A 459-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121899387</v>
+        <v>121899388</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>74729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Björkstubbe</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Björkstubbe</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121899388</v>
+        <v>121899387</v>
       </c>
       <c r="B3" t="n">
-        <v>74729</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 459-2022 artfynd.xlsx
+++ b/artfynd/A 459-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121899388</v>
+        <v>121899387</v>
       </c>
       <c r="B2" t="n">
-        <v>74729</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Tallstubbe</t>
+          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121899387</v>
+        <v>121899388</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>74733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Björkstubbe</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Björkstubbe</t>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 459-2022 artfynd.xlsx
+++ b/artfynd/A 459-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>121899388</v>
       </c>
       <c r="B3" t="n">
-        <v>74733</v>
+        <v>74737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 459-2022 artfynd.xlsx
+++ b/artfynd/A 459-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>121899388</v>
       </c>
       <c r="B3" t="n">
-        <v>74737</v>
+        <v>74739</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
